--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_10_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_10_IN_Piura.xlsx
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>24.45</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" s="29">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>47.04</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>23.8</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>3.63</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>1.09</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1919,11 +1919,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>150.2143</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1944,11 +1944,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>107.3846</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>71.49</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1969,11 +1969,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>42.8297</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>28.51</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2167,11 +2167,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>150.2496</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2290,6 +2290,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2407,6 +2408,7 @@
       <c r="F12" s="17" t="inlineStr"/>
       <c r="G12" s="17" t="inlineStr"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
@@ -2451,6 +2453,7 @@
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="8" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="96" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
@@ -2868,11 +2871,11 @@
       </c>
       <c r="B18" s="33">
         <f>SUM(B10:B17)</f>
-        <v/>
+        <v>523.87</v>
       </c>
       <c r="C18" s="23">
         <f>SUM(C10:C17)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -2882,19 +2885,19 @@
       <c r="E18" s="17" t="inlineStr"/>
       <c r="F18" s="17">
         <f>ROUND(AVERAGE(F10:F17),2)</f>
-        <v/>
+        <v>28.06</v>
       </c>
       <c r="G18" s="22">
         <f>ROUND(AVERAGE(G10:G17),4)</f>
-        <v/>
+        <v>0.5477</v>
       </c>
       <c r="H18" s="23">
         <f>ROUND(AVERAGE(H10:H17),2)</f>
-        <v/>
+        <v>72.48</v>
       </c>
       <c r="I18" s="23">
         <f>ROUND(AVERAGE(I10:I17),2)</f>
-        <v/>
+        <v>31.88</v>
       </c>
     </row>
     <row r="19"/>
